--- a/testcases/login_testcase.xlsx
+++ b/testcases/login_testcase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rjcstest\Frappe-CRM-Test-Automation\testcases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AACBF1D-C44A-4E83-B367-996AD45BE08B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B840FBFF-51D5-403F-A1E4-6CA4834FFFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2CC33F04-3AC1-4A08-AF7D-43440F4CE2E3}"/>
   </bookViews>
@@ -111,9 +111,6 @@
     <t>login_008</t>
   </si>
   <si>
-    <t>用户名首尾空格处理</t>
-  </si>
-  <si>
     <t>login_009</t>
   </si>
   <si>
@@ -240,15 +237,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.限制输入长度；或返回参数长度错误；
-2.不允许登录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成功登录首页</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>通过</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -284,6 +272,19 @@
   </si>
   <si>
     <t>失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.提示长度过长；
+2.不允许登录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.成功登录首页</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户名首尾空格处理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -702,22 +703,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
@@ -734,19 +735,19 @@
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
@@ -763,19 +764,19 @@
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" t="s">
         <v>59</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
@@ -792,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
@@ -821,19 +822,19 @@
         <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
@@ -850,19 +851,19 @@
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
@@ -879,19 +880,19 @@
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="41.4" x14ac:dyDescent="0.25">
@@ -902,54 +903,54 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="H10" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
